--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104703_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104703_W28.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0531</v>
+        <v>2.2643</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5793</v>
+        <v>3.5334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4738</v>
+        <v>-1.269</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1234</v>
+        <v>1.7847</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.7981</v>
+        <v>1.3212</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3253</v>
+        <v>0.4635</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6618000000000001</v>
+        <v>2.8738</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3912</v>
+        <v>2.2408</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.053</v>
+        <v>0.633</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4615</v>
+        <v>-1.0891</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.1893</v>
+        <v>-0.9196</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7277</v>
+        <v>-0.1695</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0423</v>
+        <v>-0.5203</v>
       </c>
       <c r="T2" t="n">
-        <v>2.468</v>
+        <v>-0.2023</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5743</v>
+        <v>-0.3181</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7199</v>
+        <v>1.2539</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1949</v>
+        <v>0.9266</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.475</v>
+        <v>0.3273</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7803</v>
+        <v>0.5111</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3218</v>
+        <v>1.2751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4585</v>
+        <v>-0.764</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8856</v>
+        <v>0.8818</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2512</v>
+        <v>0.8446</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6344</v>
+        <v>0.0372</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1053</v>
+        <v>-0.3708</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9294</v>
+        <v>0.4305</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1759</v>
+        <v>-0.8012</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0604</v>
+        <v>0.0615</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5565</v>
+        <v>0.2739</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5039</v>
+        <v>-0.2124</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>-0.2292</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2585</v>
+        <v>0.6304</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0995</v>
+        <v>1.2564</v>
       </c>
       <c r="F4" t="n">
-        <v>0.159</v>
+        <v>-0.626</v>
       </c>
       <c r="G4" t="n">
-        <v>0.505</v>
+        <v>-1.5266</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2726</v>
+        <v>-1.89</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7675999999999999</v>
+        <v>0.3634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8858</v>
+        <v>0.1242</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8485</v>
+        <v>-0.3522</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.4764</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3808</v>
+        <v>-1.6508</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4241</v>
+        <v>-1.5378</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.805</v>
+        <v>-0.113</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0711</v>
+        <v>0.9977</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4386</v>
+        <v>0.6361</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3675</v>
+        <v>0.3616</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2249</v>
+        <v>0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2249</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1699</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5495</v>
+        <v>0.2873</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3796</v>
+        <v>0.2213</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.528</v>
+        <v>-2.1195</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8932</v>
+        <v>-1.787</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3652</v>
+        <v>-0.3325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1494</v>
+        <v>-0.6832</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.333</v>
+        <v>0.3825</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4824</v>
+        <v>-1.0656</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6774</v>
+        <v>-1.4364</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5602</v>
+        <v>-2.1695</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1172</v>
+        <v>0.7331</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5391</v>
+        <v>1.49</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8953</v>
+        <v>1.1981</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6439</v>
+        <v>0.2919</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2703</v>
+        <v>-0.2959</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8122</v>
+        <v>0.6344</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0825</v>
+        <v>-0.9302</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4596</v>
+        <v>-0.4445</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3289</v>
+        <v>1.3352</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7885</v>
+        <v>-1.7797</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8556</v>
+        <v>1.8471</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8183</v>
+        <v>1.8099</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3152</v>
+        <v>-2.2916</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2643</v>
+        <v>-0.3066</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>-0.0746</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3551</v>
+        <v>-0.232</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1221</v>
+        <v>-0.3595</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5944</v>
+        <v>-1.2112</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5276999999999999</v>
+        <v>0.8517</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7515</v>
+        <v>0.5034</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9411</v>
+        <v>1.4703</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8105</v>
+        <v>-0.9668</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2714</v>
+        <v>-0.1286</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3046</v>
+        <v>1.4134</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.576</v>
+        <v>-1.542</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4801</v>
+        <v>0.632</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2457</v>
+        <v>0.0568</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2345</v>
+        <v>0.5752</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2134</v>
+        <v>0.5029</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7561</v>
+        <v>0.1043</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4573</v>
+        <v>0.3986</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0965</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1892</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3067</v>
+        <v>-1.1845</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9171</v>
+        <v>-0.3199</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6105</v>
+        <v>-0.8646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.501</v>
+        <v>-1.7563</v>
       </c>
       <c r="H8" t="n">
-        <v>1.466</v>
+        <v>-0.9257</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9649</v>
+        <v>-0.8306</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1154</v>
+        <v>-0.3083</v>
       </c>
       <c r="K8" t="n">
-        <v>1.42</v>
+        <v>0.2963</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5354</v>
+        <v>-0.6046</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6165</v>
+        <v>-1.448</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>-1.2219</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5705</v>
+        <v>-0.226</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4467</v>
+        <v>1.1684</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>1.0889</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1793</v>
+        <v>0.0795</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.0863</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.1758</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7069</v>
+        <v>-1.257</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1034</v>
+        <v>0.3128</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6035</v>
+        <v>-1.5698</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1289</v>
+        <v>1.1394</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0618</v>
+        <v>2.0703</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9329</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1882</v>
+        <v>2.1717</v>
       </c>
       <c r="K9" t="n">
-        <v>2.788</v>
+        <v>2.7751</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0593</v>
+        <v>-1.0323</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6109</v>
+        <v>-0.1672</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1179</v>
+        <v>0.3295</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.493</v>
+        <v>-0.4967</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7201</v>
+        <v>-1.425</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4019</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.122</v>
+        <v>-2.1494</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3819</v>
+        <v>-1.3994</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0433</v>
+        <v>-1.0426</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3387</v>
+        <v>-0.3568</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8627</v>
+        <v>1.8118</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3299</v>
+        <v>1.3022</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.2446</v>
+        <v>-3.2112</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5761</v>
+        <v>-1.5522</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.4809</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0998</v>
+        <v>0.2783</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.7592</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0053</v>
+        <v>-3.0151</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0374</v>
+        <v>-1.4276</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9679</v>
+        <v>-1.5875</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1798</v>
+        <v>-0.1907</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3956</v>
+        <v>1.3822</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5753</v>
+        <v>-1.5729</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8818</v>
+        <v>1.8456</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5935</v>
+        <v>2.5608</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0615</v>
+        <v>-2.0364</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.198</v>
+        <v>-1.1786</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8502</v>
+        <v>0.1544</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6775</v>
+        <v>-0.0166</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1727</v>
+        <v>0.171</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2647</v>
+        <v>-3.924</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8029</v>
+        <v>-3.4692</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4618</v>
+        <v>-0.4549</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2587</v>
+        <v>-4.2518</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9957</v>
+        <v>-1.9906</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.263</v>
+        <v>-2.2612</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6103</v>
+        <v>-2.6327</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1123</v>
+        <v>-1.1279</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6484</v>
+        <v>-1.6191</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8834</v>
+        <v>-0.8628</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9645</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0434</v>
+        <v>-0.6692</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0789</v>
+        <v>0.0457</v>
       </c>
       <c r="V12" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.194700000000001</v>
+        <v>-6.803799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1821000000000002</v>
+        <v>1.247300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.3767</v>
+        <v>-8.0511</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.7677</v>
+        <v>-7.7502</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1753</v>
+        <v>1.218400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.943</v>
+        <v>-8.968499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>8.0502</v>
+        <v>7.8032</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5028</v>
+        <v>11.3529</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.4527</v>
+        <v>-3.5497</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.8176</v>
+        <v>-15.5537</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.3275</v>
+        <v>-10.1346</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.4903</v>
+        <v>-5.418900000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.268199999999999</v>
+        <v>-2.276199999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8771000000000001</v>
+        <v>2.2764</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5275</v>
+        <v>2.9464</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6505</v>
+        <v>-0.6700999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9642000000000001</v>
+        <v>0.9465</v>
       </c>
       <c r="W13" t="n">
-        <v>7.6169</v>
+        <v>7.569800000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.652699999999999</v>
+        <v>-6.623199999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.9733</v>
+        <v>9.389699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.1203</v>
+        <v>9.891400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.147</v>
+        <v>-0.5018</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2493</v>
+        <v>5.2442</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7446</v>
+        <v>0.7412</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5047</v>
+        <v>4.503</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0944</v>
+        <v>7.0485</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8084</v>
+        <v>2.7816</v>
       </c>
       <c r="L14" t="n">
-        <v>4.286</v>
+        <v>4.2669</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8451</v>
+        <v>-1.8043</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0638</v>
+        <v>-2.0405</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2187</v>
+        <v>0.2361</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3421</v>
+        <v>-0.9244</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7984</v>
+        <v>0.0297</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5437</v>
+        <v>-0.9542</v>
       </c>
       <c r="V14" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1521</v>
+        <v>6.115</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8105</v>
+        <v>5.2642</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3417</v>
+        <v>0.8508</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7732</v>
+        <v>6.7433</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7536</v>
+        <v>2.7243</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0196</v>
+        <v>4.019</v>
       </c>
       <c r="J15" t="n">
-        <v>7.5875</v>
+        <v>7.5294</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7466</v>
+        <v>3.7017</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8409</v>
+        <v>3.8277</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8143</v>
+        <v>-0.7861</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6472</v>
+        <v>0.648</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8257</v>
+        <v>0.3573</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1785</v>
+        <v>0.2908</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1895</v>
+        <v>4.7548</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7563</v>
+        <v>6.1258</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5669</v>
+        <v>-1.371</v>
       </c>
       <c r="G16" t="n">
-        <v>4.0773</v>
+        <v>4.0666</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6294</v>
+        <v>3.6058</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4479</v>
+        <v>0.4609</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3793</v>
+        <v>5.341</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2674</v>
+        <v>5.2293</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.302</v>
+        <v>-1.2744</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O16" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1406</v>
+        <v>-0.2938</v>
       </c>
       <c r="T16" t="n">
-        <v>0.738</v>
+        <v>0.1506</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.4444</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7407</v>
+        <v>3.7277</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1998</v>
+        <v>1.0688</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5409</v>
+        <v>2.6589</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9716</v>
       </c>
       <c r="H17" t="n">
-        <v>0.798</v>
+        <v>0.7957</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1733</v>
+        <v>0.1759</v>
       </c>
       <c r="J17" t="n">
-        <v>0.968</v>
+        <v>0.9568</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0033</v>
+        <v>0.0148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.796</v>
+        <v>0.7758</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4567</v>
+        <v>0.3412</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3393</v>
+        <v>0.4345</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1573</v>
+        <v>0.384</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.8281</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1573</v>
+        <v>-1.444</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1573</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1573</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.0193</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.9921</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.9997</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.0077</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1573</v>
+        <v>-1.664</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1573</v>
+        <v>-1.6524</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.0116</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.4692</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.0258</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.4433</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0138</v>
+        <v>0.1579</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1265</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1403</v>
+        <v>0.1579</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7578</v>
+        <v>0.1579</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1124</v>
+        <v>0.1579</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3546</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8131</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.773</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9447</v>
+        <v>0.1579</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3393</v>
+        <v>0.1579</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3946</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0415</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3692</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9134</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4558</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1759</v>
+        <v>-0.6803</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4864</v>
+        <v>-1.2546</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6623</v>
+        <v>0.5743</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6867</v>
+        <v>0.1942</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6654</v>
+        <v>-0.5492</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0213</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0017</v>
+        <v>0.6805</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0044</v>
+        <v>0.2413</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0027</v>
+        <v>0.4392</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6884</v>
+        <v>-0.4863</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6698</v>
+        <v>-0.7906</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0186</v>
+        <v>0.3043</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.009</v>
+        <v>-0.1021</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3811</v>
+        <v>-0.3417</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6279</v>
+        <v>0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7071</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.861</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5959</v>
+        <v>-0.6241</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7349</v>
+        <v>-0.196</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1795</v>
+        <v>-1.7585</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5615</v>
+        <v>-2.1192</v>
       </c>
       <c r="I21" t="n">
-        <v>0.741</v>
+        <v>0.3608</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6875</v>
+        <v>-0.842</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2424</v>
+        <v>-0.7971</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4451</v>
+        <v>-0.0449</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.508</v>
+        <v>-0.9164</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.3221</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2959</v>
+        <v>0.4057</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2674</v>
+        <v>0.5239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>0.4455</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4282</v>
+        <v>0.0784</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-1.6342</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9393</v>
+        <v>-1.7072</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0121</v>
+        <v>-2.673</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0728</v>
+        <v>0.9658</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4389</v>
+        <v>-1.4307</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2021</v>
+        <v>-1.2006</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3249</v>
+        <v>-1.3324</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1732</v>
+        <v>0.1724</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.114</v>
+        <v>-0.0982</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2075</v>
+        <v>0.021</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2794</v>
+        <v>0.1535</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2413</v>
+        <v>-2.4866</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4256</v>
+        <v>-3.4447</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1843</v>
+        <v>0.9581</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2303</v>
+        <v>-3.2356</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2654</v>
+        <v>-2.2688</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9649</v>
+        <v>-0.9668</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2018</v>
+        <v>-3.2215</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6664</v>
+        <v>-1.6795</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0285</v>
+        <v>-0.0141</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1744</v>
+        <v>0.928</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2299</v>
+        <v>0.232</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9445</v>
+        <v>0.6959</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3656</v>
+        <v>-4.2743</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0076</v>
+        <v>-4.0235</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.358</v>
+        <v>-0.2508</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7028</v>
+        <v>-1.6997</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0706</v>
+        <v>-2.0708</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3679</v>
+        <v>0.3711</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3915</v>
+        <v>-1.3986</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3113</v>
+        <v>-0.3011</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4606</v>
+        <v>-0.3681</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3396</v>
+        <v>-0.2473</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4491</v>
+        <v>-5.5732</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.829</v>
+        <v>-4.1073</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6201</v>
+        <v>-1.4659</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8237</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3462</v>
+        <v>-1.3524</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5224</v>
+        <v>0.5213</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1694</v>
+        <v>-0.2001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1345</v>
+        <v>0.1132</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6543</v>
+        <v>-0.631</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R25" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.718</v>
+        <v>-0.8316</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0302</v>
+        <v>-0.2652</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6878</v>
+        <v>-0.5664</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.1945</v>
+        <v>8.987400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>8.3766</v>
+        <v>8.051100000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1821000000000004</v>
+        <v>0.9363000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>7.767700000000002</v>
+        <v>7.7503</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.175399999999999</v>
+        <v>-1.218300000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>8.943099999999999</v>
+        <v>8.9687</v>
       </c>
       <c r="J26" t="n">
-        <v>15.8177</v>
+        <v>15.5537</v>
       </c>
       <c r="K26" t="n">
-        <v>10.3275</v>
+        <v>10.1346</v>
       </c>
       <c r="L26" t="n">
-        <v>5.4905</v>
+        <v>5.419099999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.049999999999999</v>
+        <v>-7.8032</v>
       </c>
       <c r="N26" t="n">
-        <v>-11.5027</v>
+        <v>-11.353</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4526</v>
+        <v>3.5496</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2683</v>
+        <v>2.276199999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8771999999999996</v>
+        <v>-0.0924999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6505</v>
+        <v>0.6701</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5276</v>
+        <v>-0.7629</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9643000000000002</v>
+        <v>-0.9466000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>6.6526</v>
+        <v>6.6232</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.617000000000001</v>
+        <v>-7.5697</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104703_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104703_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.623199999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104703_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.5697</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
